--- a/resources/templates/Checklist_Positions/Template_ADAS3.xlsx
+++ b/resources/templates/Checklist_Positions/Template_ADAS3.xlsx
@@ -1032,19 +1032,19 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>KIANNE CAILA R. ABAT</t>
+    <t>${encoder_name}</t>
   </si>
   <si>
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Aide I</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t>Date: January 21, 2026</t>
+    <t>Date: ${date_of_signing}</t>
   </si>
   <si>
     <t>APC Form - (Revised 2018)</t>
@@ -1409,14 +1409,6 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="8.5"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1428,6 +1420,14 @@
       <i/>
       <sz val="8.5"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
